--- a/Email_Structural.xlsx
+++ b/Email_Structural.xlsx
@@ -2433,12 +2433,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>شيخ</t>
+          <t>Shaik</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>نور أحمد</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -13478,12 +13478,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>عبدالله</t>
+          <t>Abdullah</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>نصر</t>
+          <t>Nasr</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
